--- a/public/exports-with-coowners/29189919.xlsx
+++ b/public/exports-with-coowners/29189919.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports-with-coowners/29189919.xlsx
+++ b/public/exports-with-coowners/29189919.xlsx
@@ -7551,20 +7551,20 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4455442</t>
+          <t xml:space="preserve">4455442, 100194390</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J101">
-        <v>2812</v>
+        <v>1173</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311465122</t>
+          <t xml:space="preserve">311465121</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7616,30 +7616,30 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevejen 6</t>
+          <t xml:space="preserve">Skolegade 31</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">7280</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4455442</t>
+          <t xml:space="preserve">9455769</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J102">
-        <v>386</v>
+        <v>1152</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311465119</t>
+          <t xml:space="preserve">311465344</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-04</t>
+          <t xml:space="preserve">2030-10-05</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7691,30 +7691,30 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevejen 6</t>
+          <t xml:space="preserve">Kollundvej 15</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4455442, 100194390</t>
+          <t xml:space="preserve">4453257</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J103">
-        <v>1173</v>
+        <v>282</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311465121</t>
+          <t xml:space="preserve">311471519</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-04</t>
+          <t xml:space="preserve">2030-10-30</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 31</t>
+          <t xml:space="preserve">Skolegade 13B</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7781,15 +7781,15 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J104">
-        <v>1152</v>
+        <v>725</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311465344</t>
+          <t xml:space="preserve">311471524</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-05</t>
+          <t xml:space="preserve">2030-10-30</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,30 +7841,30 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kollundvej 15</t>
+          <t xml:space="preserve">Soldalen 4</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4453257</t>
+          <t xml:space="preserve">4462904</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J105">
-        <v>282</v>
+        <v>380</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311471519</t>
+          <t xml:space="preserve">311471529</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7916,30 +7916,30 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 13B</t>
+          <t xml:space="preserve">Brændgårdvej 20</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">7280</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">9455769</t>
+          <t xml:space="preserve">5706289</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J106">
-        <v>725</v>
+        <v>7818</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311471524</t>
+          <t xml:space="preserve">311475497</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-30</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,17 +7991,17 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soldalen 4</t>
+          <t xml:space="preserve">Bethaniagade 10</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">4462904</t>
+          <t xml:space="preserve">8591744</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -8010,21 +8010,21 @@
         </is>
       </c>
       <c r="J107">
-        <v>380</v>
+        <v>3391</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311471529</t>
+          <t xml:space="preserve">311868826</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-30</t>
+          <t xml:space="preserve">2030-12-07</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændgårdvej 20</t>
+          <t xml:space="preserve">Torvet 5</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706289</t>
+          <t xml:space="preserve">5697356</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -8085,11 +8085,11 @@
         </is>
       </c>
       <c r="J108">
-        <v>7818</v>
+        <v>2786</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475497</t>
+          <t xml:space="preserve">311480990</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-12-07</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8141,30 +8141,30 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyvelvej 5</t>
+          <t xml:space="preserve">Bethaniagade 1</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">7550</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4506406</t>
+          <t xml:space="preserve">5697356</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J109">
-        <v>498</v>
+        <v>3979</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475754</t>
+          <t xml:space="preserve">311481616</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-15</t>
+          <t xml:space="preserve">2030-12-09</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bethaniagade 10</t>
+          <t xml:space="preserve">Brorsonsvej 6</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,30 +8226,30 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8591744</t>
+          <t xml:space="preserve">5706491</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J110">
-        <v>3391</v>
+        <v>1380</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868826</t>
+          <t xml:space="preserve">311481632</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-07</t>
+          <t xml:space="preserve">2030-12-09</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 5</t>
+          <t xml:space="preserve">H.P. Hansens Vej 6B</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8301,20 +8301,20 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697356</t>
+          <t xml:space="preserve">5704686</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J111">
-        <v>2786</v>
+        <v>285</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311480990</t>
+          <t xml:space="preserve">311482350</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-07</t>
+          <t xml:space="preserve">2030-12-11</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bethaniagade 1</t>
+          <t xml:space="preserve">Asylgade 1</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8376,20 +8376,20 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697356</t>
+          <t xml:space="preserve">4457628</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J112">
-        <v>3979</v>
+        <v>278</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481616</t>
+          <t xml:space="preserve">311482554</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-09</t>
+          <t xml:space="preserve">2030-12-14</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brorsonsvej 6</t>
+          <t xml:space="preserve">Hammershusvej 7</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8451,20 +8451,20 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706491</t>
+          <t xml:space="preserve">5704845</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J113">
-        <v>1380</v>
+        <v>1208</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481632</t>
+          <t xml:space="preserve">311483577</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-09</t>
+          <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">H.P. Hansens Vej 6B</t>
+          <t xml:space="preserve">Hammershusvej 7</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8526,20 +8526,20 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704686</t>
+          <t xml:space="preserve">5704845</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J114">
-        <v>285</v>
+        <v>634</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482350</t>
+          <t xml:space="preserve">311483578</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-11</t>
+          <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asylgade 1</t>
+          <t xml:space="preserve">Engbjerg 21</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">4457628</t>
+          <t xml:space="preserve">4456901</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -8610,11 +8610,11 @@
         </is>
       </c>
       <c r="J115">
-        <v>278</v>
+        <v>2078</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482554</t>
+          <t xml:space="preserve">311488098</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-14</t>
+          <t xml:space="preserve">2031-01-15</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hammershusvej 7</t>
+          <t xml:space="preserve">Engbjerg 21</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,20 +8676,20 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704845</t>
+          <t xml:space="preserve">4456901</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J116">
-        <v>1208</v>
+        <v>1199</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483577</t>
+          <t xml:space="preserve">311488100</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-17</t>
+          <t xml:space="preserve">2031-01-15</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hammershusvej 7</t>
+          <t xml:space="preserve">Engbjerg 21</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,20 +8751,20 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704845</t>
+          <t xml:space="preserve">4456901</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J117">
-        <v>634</v>
+        <v>587</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483578</t>
+          <t xml:space="preserve">311488102</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-17</t>
+          <t xml:space="preserve">2031-01-15</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engbjerg 21</t>
+          <t xml:space="preserve">Engbjerg 23</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8831,15 +8831,15 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J118">
-        <v>2078</v>
+        <v>1174</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311488098</t>
+          <t xml:space="preserve">311488103</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8891,30 +8891,30 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engbjerg 21</t>
+          <t xml:space="preserve">Jernbanegade 2</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7490</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456901</t>
+          <t xml:space="preserve">4435005</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J119">
-        <v>1199</v>
+        <v>309</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311488100</t>
+          <t xml:space="preserve">311488032</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engbjerg 21</t>
+          <t xml:space="preserve">Vesterlindvej 21</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456901</t>
+          <t xml:space="preserve">4452247</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8985,16 +8985,16 @@
         </is>
       </c>
       <c r="J120">
-        <v>587</v>
+        <v>482</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311488102</t>
+          <t xml:space="preserve">311488095</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engbjerg 23</t>
+          <t xml:space="preserve">Gl. Skolevej 35</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9051,20 +9051,20 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456901</t>
+          <t xml:space="preserve">5699393</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J121">
-        <v>1174</v>
+        <v>3690</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311488103</t>
+          <t xml:space="preserve">311500097</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-15</t>
+          <t xml:space="preserve">2031-03-03</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,30 +9116,30 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 2</t>
+          <t xml:space="preserve">Gl. Skolevej 35</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">7490</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">4435005</t>
+          <t xml:space="preserve">5699393</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J122">
-        <v>309</v>
+        <v>3682</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311488032</t>
+          <t xml:space="preserve">311500098</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-15</t>
+          <t xml:space="preserve">2031-03-03</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterlindvej 21</t>
+          <t xml:space="preserve">Gl. Skolevej 35</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">4452247</t>
+          <t xml:space="preserve">5699393</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -9210,21 +9210,21 @@
         </is>
       </c>
       <c r="J123">
-        <v>482</v>
+        <v>1529</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311488095</t>
+          <t xml:space="preserve">311500100</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-15</t>
+          <t xml:space="preserve">2031-03-03</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,17 +9266,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Skolevej 35</t>
+          <t xml:space="preserve">Soldalen 8</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699393</t>
+          <t xml:space="preserve">8453536</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9285,11 +9285,11 @@
         </is>
       </c>
       <c r="J124">
-        <v>3690</v>
+        <v>2260</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311500097</t>
+          <t xml:space="preserve">311500079</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9356,15 +9356,15 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J125">
-        <v>3682</v>
+        <v>1438</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311500098</t>
+          <t xml:space="preserve">311502543</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-03</t>
+          <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,30 +9416,30 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Skolevej 35</t>
+          <t xml:space="preserve">Skalmejevej 33</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7451</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699393</t>
+          <t xml:space="preserve">1805456</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J126">
-        <v>1529</v>
+        <v>4065</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311500100</t>
+          <t xml:space="preserve">311502547</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-03</t>
+          <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,30 +9491,30 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soldalen 8</t>
+          <t xml:space="preserve">Skalmejevej 33</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7451</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">8453536</t>
+          <t xml:space="preserve">1805456</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J127">
-        <v>2260</v>
+        <v>582</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311500079</t>
+          <t xml:space="preserve">311502548</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-03</t>
+          <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Skolevej 35</t>
+          <t xml:space="preserve">Tjelevej 25</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9576,20 +9576,20 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699393</t>
+          <t xml:space="preserve">5707346</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J128">
-        <v>1438</v>
+        <v>1821</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502543</t>
+          <t xml:space="preserve">311507310</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-11</t>
+          <t xml:space="preserve">2031-03-26</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9641,30 +9641,30 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skalmejevej 33</t>
+          <t xml:space="preserve">Tjelevej 25</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">7451</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805456</t>
+          <t xml:space="preserve">5707346</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J129">
-        <v>4065</v>
+        <v>914</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502547</t>
+          <t xml:space="preserve">311507300</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-11</t>
+          <t xml:space="preserve">2031-03-26</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,17 +9716,17 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skalmejevej 33</t>
+          <t xml:space="preserve">Tjelevej 25</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">7451</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805456</t>
+          <t xml:space="preserve">5707346</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -9735,11 +9735,11 @@
         </is>
       </c>
       <c r="J130">
-        <v>582</v>
+        <v>1214</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502548</t>
+          <t xml:space="preserve">311507302</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-11</t>
+          <t xml:space="preserve">2031-03-26</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9806,15 +9806,15 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J131">
-        <v>1821</v>
+        <v>1296</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507310</t>
+          <t xml:space="preserve">311507304</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9881,15 +9881,15 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J132">
-        <v>914</v>
+        <v>1390</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507300</t>
+          <t xml:space="preserve">311507307</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9956,15 +9956,15 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J133">
-        <v>1214</v>
+        <v>4684</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507302</t>
+          <t xml:space="preserve">311507298</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10016,40 +10016,40 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjelevej 25</t>
+          <t xml:space="preserve">Velhustedvej 10</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5707346</t>
+          <t xml:space="preserve">1805364</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J134">
-        <v>1296</v>
+        <v>1515</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507304</t>
+          <t xml:space="preserve">311873970</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-26</t>
+          <t xml:space="preserve">2031-04-09</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10091,30 +10091,30 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjelevej 25</t>
+          <t xml:space="preserve">Velhustedvej 10</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5707346</t>
+          <t xml:space="preserve">1805364</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J135">
-        <v>1390</v>
+        <v>701</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507307</t>
+          <t xml:space="preserve">311511168</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-26</t>
+          <t xml:space="preserve">2031-04-09</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10166,30 +10166,30 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjelevej 25</t>
+          <t xml:space="preserve">Velhustedvej 6</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5707346</t>
+          <t xml:space="preserve">1805364</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J136">
-        <v>4684</v>
+        <v>413</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507298</t>
+          <t xml:space="preserve">311511163</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-26</t>
+          <t xml:space="preserve">2031-04-09</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10256,25 +10256,25 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J137">
-        <v>1515</v>
+        <v>1096</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873970</t>
+          <t xml:space="preserve">311511782</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-09</t>
+          <t xml:space="preserve">2031-04-13</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10331,15 +10331,15 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J138">
-        <v>701</v>
+        <v>423</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311511168</t>
+          <t xml:space="preserve">311511784</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-09</t>
+          <t xml:space="preserve">2031-04-13</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velhustedvej 6</t>
+          <t xml:space="preserve">Velhustedvej 12A</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10406,15 +10406,15 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J139">
-        <v>413</v>
+        <v>1052</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311511163</t>
+          <t xml:space="preserve">311513130</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-09</t>
+          <t xml:space="preserve">2031-04-16</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herning Kommune</t>
+          <t xml:space="preserve">MCH A/S</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -10466,40 +10466,40 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velhustedvej 10</t>
+          <t xml:space="preserve">Kaj Zartows Vej 5</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805364</t>
+          <t xml:space="preserve">100291056, 100291057, 100291058</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J140">
-        <v>1096</v>
+        <v>11483</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311511782</t>
+          <t xml:space="preserve">311532840</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+          <t xml:space="preserve">Scanenergi A/S</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-13</t>
+          <t xml:space="preserve">2031-07-01</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velhustedvej 10</t>
+          <t xml:space="preserve">Jernbanegade 1</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10551,20 +10551,20 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805364</t>
+          <t xml:space="preserve">4433294</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J141">
-        <v>423</v>
+        <v>324</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311511784</t>
+          <t xml:space="preserve">311535258</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-13</t>
+          <t xml:space="preserve">2031-07-12</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,30 +10616,30 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velhustedvej 12A</t>
+          <t xml:space="preserve">Burgårdsvej 8</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805364</t>
+          <t xml:space="preserve">4462912</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J142">
-        <v>1052</v>
+        <v>848</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513130</t>
+          <t xml:space="preserve">311539387</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-16</t>
+          <t xml:space="preserve">2031-08-06</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">MCH A/S</t>
+          <t xml:space="preserve">Herning Kommune</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaj Zartows Vej 5</t>
+          <t xml:space="preserve">Brorsonsvej 4</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">100291056, 100291057, 100291058</t>
+          <t xml:space="preserve">5706491</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -10710,21 +10710,21 @@
         </is>
       </c>
       <c r="J143">
-        <v>11483</v>
+        <v>4954</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311532840</t>
+          <t xml:space="preserve">311543939</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scanenergi A/S</t>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-01</t>
+          <t xml:space="preserve">2031-08-27</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,17 +10766,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 1</t>
+          <t xml:space="preserve">Brorsonsvej 2</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433294</t>
+          <t xml:space="preserve">5706423</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -10785,11 +10785,11 @@
         </is>
       </c>
       <c r="J144">
-        <v>324</v>
+        <v>9030</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535258</t>
+          <t xml:space="preserve">311547312</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-12</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,30 +10841,30 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Burgårdsvej 8</t>
+          <t xml:space="preserve">Brorsonsvej 2</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4462912</t>
+          <t xml:space="preserve">5706423</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J145">
-        <v>848</v>
+        <v>802</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539387</t>
+          <t xml:space="preserve">311548281</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-06</t>
+          <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,30 +10916,30 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brorsonsvej 4</t>
+          <t xml:space="preserve">Midgaardsvej 20</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706491</t>
+          <t xml:space="preserve">8748212</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J146">
-        <v>4954</v>
+        <v>320</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543939</t>
+          <t xml:space="preserve">311549309</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-27</t>
+          <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,17 +10991,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brorsonsvej 2</t>
+          <t xml:space="preserve">Fuglsangsvej 15</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706423</t>
+          <t xml:space="preserve">739998, 4503192</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -11010,21 +11010,21 @@
         </is>
       </c>
       <c r="J147">
-        <v>9030</v>
+        <v>369</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547312</t>
+          <t xml:space="preserve">311553193</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+          <t xml:space="preserve">Graugaard Consult aps</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-10</t>
+          <t xml:space="preserve">2031-10-05</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brorsonsvej 2</t>
+          <t xml:space="preserve">Valeursvej 11</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -11076,20 +11076,20 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706423</t>
+          <t xml:space="preserve">5704408</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J148">
-        <v>802</v>
+        <v>1491</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548281</t>
+          <t xml:space="preserve">311553355</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-15</t>
+          <t xml:space="preserve">2031-10-06</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,40 +11141,40 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midgaardsvej 20</t>
+          <t xml:space="preserve">Brændgårdvej 103C</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">8748212</t>
+          <t xml:space="preserve">9868104</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J149">
-        <v>320</v>
+        <v>269</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549309</t>
+          <t xml:space="preserve">311554956</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-20</t>
+          <t xml:space="preserve">2031-10-13</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,17 +11216,17 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsangsvej 15</t>
+          <t xml:space="preserve">Fyrrevej 8</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">739998, 4503192</t>
+          <t xml:space="preserve">5701206</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -11235,21 +11235,21 @@
         </is>
       </c>
       <c r="J150">
-        <v>369</v>
+        <v>400</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311553193</t>
+          <t xml:space="preserve">311555699</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Graugaard Consult aps</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-05</t>
+          <t xml:space="preserve">2031-10-15</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valeursvej 11</t>
+          <t xml:space="preserve">Lyngens Kvarter 225</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11301,30 +11301,30 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704408</t>
+          <t xml:space="preserve">8966751</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J151">
-        <v>1491</v>
+        <v>353</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311553355</t>
+          <t xml:space="preserve">311555700</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-06</t>
+          <t xml:space="preserve">2031-10-15</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændgårdvej 103C</t>
+          <t xml:space="preserve">Mørupvej 32</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11376,20 +11376,20 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">9868104</t>
+          <t xml:space="preserve">5700249</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J152">
-        <v>269</v>
+        <v>1238</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311554956</t>
+          <t xml:space="preserve">311555794</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-13</t>
+          <t xml:space="preserve">2031-10-15</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,17 +11441,17 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fyrrevej 8</t>
+          <t xml:space="preserve">Østre Søvej 2</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7451</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5701206</t>
+          <t xml:space="preserve">4459086</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -11460,11 +11460,11 @@
         </is>
       </c>
       <c r="J153">
-        <v>400</v>
+        <v>304</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555695</t>
+          <t xml:space="preserve">311555714</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngens Kvarter 225</t>
+          <t xml:space="preserve">Lindegårdsvej 10</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11526,30 +11526,30 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">8966751</t>
+          <t xml:space="preserve">5699836</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J154">
-        <v>353</v>
+        <v>617</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555700</t>
+          <t xml:space="preserve">311559404</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-15</t>
+          <t xml:space="preserve">2031-11-03</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mørupvej 32</t>
+          <t xml:space="preserve">Lindegårdsvej 10B</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700249</t>
+          <t xml:space="preserve">5699836</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -11610,11 +11610,11 @@
         </is>
       </c>
       <c r="J155">
-        <v>1238</v>
+        <v>824</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555794</t>
+          <t xml:space="preserve">311559406</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-15</t>
+          <t xml:space="preserve">2031-11-03</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,17 +11666,17 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Søvej 2</t>
+          <t xml:space="preserve">Lindegårdsvej 146</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">7451</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">4459086</t>
+          <t xml:space="preserve">1809289</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -11685,11 +11685,11 @@
         </is>
       </c>
       <c r="J156">
-        <v>304</v>
+        <v>771</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555714</t>
+          <t xml:space="preserve">311560386</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-15</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 10</t>
+          <t xml:space="preserve">Herluf Trolles Vej 1A</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11756,15 +11756,15 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J157">
-        <v>617</v>
+        <v>525</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559404</t>
+          <t xml:space="preserve">311561966</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-03</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 10B</t>
+          <t xml:space="preserve">Herluf Trolles Vej 1B</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11831,15 +11831,15 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J158">
-        <v>824</v>
+        <v>522</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559406</t>
+          <t xml:space="preserve">311566877</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-03</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 146</t>
+          <t xml:space="preserve">Lindegårdsvej 6</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11901,20 +11901,20 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809289</t>
+          <t xml:space="preserve">5699836</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J159">
-        <v>771</v>
+        <v>802</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560386</t>
+          <t xml:space="preserve">311561962</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herluf Trolles Vej 1A</t>
+          <t xml:space="preserve">Lindegårdsvej 8</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11981,15 +11981,15 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J160">
-        <v>525</v>
+        <v>472</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561966</t>
+          <t xml:space="preserve">311561963</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herluf Trolles Vej 1B</t>
+          <t xml:space="preserve">Kaj Zartows Vej 19</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12051,20 +12051,20 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699836</t>
+          <t xml:space="preserve">8966321</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J161">
-        <v>522</v>
+        <v>615</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566877</t>
+          <t xml:space="preserve">311566234</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2031-12-06</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,30 +12116,30 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 6</t>
+          <t xml:space="preserve">Kastanie Alle 27</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699836</t>
+          <t xml:space="preserve">9455731</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J162">
-        <v>802</v>
+        <v>1001</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561962</t>
+          <t xml:space="preserve">311566808</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2031-12-08</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 8</t>
+          <t xml:space="preserve">Vesterlindvej 21</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12201,20 +12201,20 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699836</t>
+          <t xml:space="preserve">4452247</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J163">
-        <v>472</v>
+        <v>430</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561963</t>
+          <t xml:space="preserve">311567053</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,30 +12266,30 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaj Zartows Vej 19</t>
+          <t xml:space="preserve">Solbakken 30A</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">8966321</t>
+          <t xml:space="preserve">4433142</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J164">
-        <v>615</v>
+        <v>2469</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566234</t>
+          <t xml:space="preserve">311568010</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-06</t>
+          <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,17 +12341,17 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanie Alle 27</t>
+          <t xml:space="preserve">Østergade 5</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">7490</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">9455731</t>
+          <t xml:space="preserve">4433876</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -12360,11 +12360,11 @@
         </is>
       </c>
       <c r="J165">
-        <v>1001</v>
+        <v>2190</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566808</t>
+          <t xml:space="preserve">311568091</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-08</t>
+          <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterlindvej 21</t>
+          <t xml:space="preserve">Vestergade 82</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,20 +12426,20 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">4452247</t>
+          <t xml:space="preserve">5699393</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J166">
-        <v>430</v>
+        <v>626</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567053</t>
+          <t xml:space="preserve">311568880</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-09</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12491,17 +12491,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haugevej 25</t>
+          <t xml:space="preserve">Ågårdsvej 2D</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">100063131</t>
+          <t xml:space="preserve">9888291</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -12510,11 +12510,11 @@
         </is>
       </c>
       <c r="J167">
-        <v>1683</v>
+        <v>948</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567248</t>
+          <t xml:space="preserve">311568878</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-10</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12566,17 +12566,17 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solbakken 30A</t>
+          <t xml:space="preserve">Dueoddevej 9</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433142</t>
+          <t xml:space="preserve">5705804</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -12585,11 +12585,11 @@
         </is>
       </c>
       <c r="J168">
-        <v>2469</v>
+        <v>1962</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568010</t>
+          <t xml:space="preserve">311571890</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-15</t>
+          <t xml:space="preserve">2032-01-12</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12641,30 +12641,30 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 5</t>
+          <t xml:space="preserve">Brændgårdvej 99</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">7490</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433876</t>
+          <t xml:space="preserve">8481827</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J169">
-        <v>2190</v>
+        <v>550</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568091</t>
+          <t xml:space="preserve">311572663</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-15</t>
+          <t xml:space="preserve">2032-01-17</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 82</t>
+          <t xml:space="preserve">Ringkøbingvej 112</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699393</t>
+          <t xml:space="preserve">100002469</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -12735,11 +12735,11 @@
         </is>
       </c>
       <c r="J170">
-        <v>626</v>
+        <v>2608</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568880</t>
+          <t xml:space="preserve">311574347</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-01-25</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12791,17 +12791,17 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågårdsvej 2D</t>
+          <t xml:space="preserve">Gisselfeldvej 2</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">9888291</t>
+          <t xml:space="preserve">5708304</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -12810,11 +12810,11 @@
         </is>
       </c>
       <c r="J171">
-        <v>948</v>
+        <v>1303</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568878</t>
+          <t xml:space="preserve">311575936</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-02-01</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dueoddevej 9</t>
+          <t xml:space="preserve">Gisselfeldvej 2</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12876,20 +12876,20 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5705804</t>
+          <t xml:space="preserve">5708304</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J172">
-        <v>1962</v>
+        <v>305</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571890</t>
+          <t xml:space="preserve">311575938</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-12</t>
+          <t xml:space="preserve">2032-02-01</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændgårdvej 99</t>
+          <t xml:space="preserve">Gyvelens Kvarter 10</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12951,20 +12951,20 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">8481827</t>
+          <t xml:space="preserve">8966750</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J173">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572663</t>
+          <t xml:space="preserve">311575933</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-17</t>
+          <t xml:space="preserve">2032-02-01</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringkøbingvej 112</t>
+          <t xml:space="preserve">Skovvænget 2B</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -13026,20 +13026,20 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">100002469</t>
+          <t xml:space="preserve">9827058</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J174">
-        <v>2608</v>
+        <v>825</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574347</t>
+          <t xml:space="preserve">311575940</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-25</t>
+          <t xml:space="preserve">2032-02-01</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gisselfeldvej 2</t>
+          <t xml:space="preserve">Museumsgade 32</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">5708304</t>
+          <t xml:space="preserve">5700031</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -13110,11 +13110,11 @@
         </is>
       </c>
       <c r="J175">
-        <v>1303</v>
+        <v>2327</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575936</t>
+          <t xml:space="preserve">311577008</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-01</t>
+          <t xml:space="preserve">2032-02-06</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gisselfeldvej 2</t>
+          <t xml:space="preserve">Skovvænget 2A</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13176,20 +13176,20 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5708304</t>
+          <t xml:space="preserve">9827058</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J176">
-        <v>305</v>
+        <v>514</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575938</t>
+          <t xml:space="preserve">311577005</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-01</t>
+          <t xml:space="preserve">2032-02-06</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyvelens Kvarter 10</t>
+          <t xml:space="preserve">Brændgårdvej 107</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13251,20 +13251,20 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">8966750</t>
+          <t xml:space="preserve">100377971</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J177">
-        <v>400</v>
+        <v>9582</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575933</t>
+          <t xml:space="preserve">311582020</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-01</t>
+          <t xml:space="preserve">2032-03-02</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvænget 2B</t>
+          <t xml:space="preserve">Brændgårdvej 20B</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -13326,20 +13326,20 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">9827058</t>
+          <t xml:space="preserve">5706289</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J178">
-        <v>825</v>
+        <v>3371</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575940</t>
+          <t xml:space="preserve">311582023</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-01</t>
+          <t xml:space="preserve">2032-03-02</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Museumsgade 32</t>
+          <t xml:space="preserve">Brændgårdvej 99</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13401,7 +13401,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700031</t>
+          <t xml:space="preserve">8481827</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -13410,11 +13410,11 @@
         </is>
       </c>
       <c r="J179">
-        <v>2327</v>
+        <v>478</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311577008</t>
+          <t xml:space="preserve">311582021</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-06</t>
+          <t xml:space="preserve">2032-03-02</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvænget 2A</t>
+          <t xml:space="preserve">Brændgårdvej 99</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -13476,20 +13476,20 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">9827058</t>
+          <t xml:space="preserve">8481827</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J180">
-        <v>514</v>
+        <v>453</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311577005</t>
+          <t xml:space="preserve">311582022</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-06</t>
+          <t xml:space="preserve">2032-03-02</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændgårdvej 107</t>
+          <t xml:space="preserve">Dalgas Plads 7A</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13551,30 +13551,30 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">100377971</t>
+          <t xml:space="preserve">334005, 334006, 334007, 334008, 334009, 334010, 334011, 334012, 334013, 334014, 334015, 334016, 334017, 334018, 334019, 334020, 334021, 334022, 334023, 334024, 334025, 334026, 334027, 334028, 334029, 334030, 334036, 334031, 334032, 334033, 334034, 334035, 334037, 334038, 334039, 334040, 334042, 100319954</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J181">
-        <v>9582</v>
+        <v>9740</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582020</t>
+          <t xml:space="preserve">311586771</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-02</t>
+          <t xml:space="preserve">2032-03-21</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændgårdvej 20B</t>
+          <t xml:space="preserve">Birk Centerpark 1</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -13626,20 +13626,20 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706289</t>
+          <t xml:space="preserve">4439896</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J182">
-        <v>3371</v>
+        <v>706</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582023</t>
+          <t xml:space="preserve">311587481</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-02</t>
+          <t xml:space="preserve">2032-03-23</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændgårdvej 99</t>
+          <t xml:space="preserve">Valdemarsvej 359</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13701,20 +13701,20 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">8481827</t>
+          <t xml:space="preserve">5704898</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J183">
-        <v>478</v>
+        <v>787</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582021</t>
+          <t xml:space="preserve">311587769</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-02</t>
+          <t xml:space="preserve">2032-03-24</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13766,30 +13766,30 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændgårdvej 99</t>
+          <t xml:space="preserve">Velhustedvej 12B</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">8481827</t>
+          <t xml:space="preserve">1805364</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J184">
-        <v>453</v>
+        <v>340</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582022</t>
+          <t xml:space="preserve">311587772</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-02</t>
+          <t xml:space="preserve">2032-03-24</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalgas Plads 7A</t>
+          <t xml:space="preserve">Engbjerg 21</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -13851,30 +13851,30 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">334005, 334006, 334007, 334008, 334009, 334010, 334011, 334012, 334013, 334014, 334015, 334016, 334017, 334018, 334019, 334020, 334021, 334022, 334023, 334024, 334025, 334026, 334027, 334028, 334029, 334030, 334036, 334031, 334032, 334033, 334034, 334035, 334037, 334038, 334039, 334040, 334042, 100319954</t>
+          <t xml:space="preserve">4456901</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J185">
-        <v>9740</v>
+        <v>625</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586771</t>
+          <t xml:space="preserve">311588514</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-21</t>
+          <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birk Centerpark 1</t>
+          <t xml:space="preserve">Engbjerg 23</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13926,20 +13926,20 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">4439896</t>
+          <t xml:space="preserve">4456901</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J186">
-        <v>706</v>
+        <v>738</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587481</t>
+          <t xml:space="preserve">311588517</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-23</t>
+          <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdemarsvej 359</t>
+          <t xml:space="preserve">Nørregade 30</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14001,20 +14001,20 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704898</t>
+          <t xml:space="preserve">7268351</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J187">
-        <v>787</v>
+        <v>6466</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587769</t>
+          <t xml:space="preserve">311596592</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-24</t>
+          <t xml:space="preserve">2032-04-29</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14066,30 +14066,30 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velhustedvej 12B</t>
+          <t xml:space="preserve">Birkmosevej 26</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805364</t>
+          <t xml:space="preserve">4503146</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J188">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587772</t>
+          <t xml:space="preserve">311598021</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-24</t>
+          <t xml:space="preserve">2032-05-05</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engbjerg 21</t>
+          <t xml:space="preserve">Valdemarsvej 343</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -14151,20 +14151,20 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456901</t>
+          <t xml:space="preserve">5704898</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J189">
-        <v>625</v>
+        <v>15574</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588514</t>
+          <t xml:space="preserve">311598704</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-05-09</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engbjerg 23</t>
+          <t xml:space="preserve">Sandagervej 35</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -14226,20 +14226,20 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456901</t>
+          <t xml:space="preserve">5700242</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J190">
-        <v>738</v>
+        <v>904</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588517</t>
+          <t xml:space="preserve">311599479</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-05-11</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 30</t>
+          <t xml:space="preserve">Fenrisvej 24</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">7268351</t>
+          <t xml:space="preserve">5702325</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -14310,11 +14310,11 @@
         </is>
       </c>
       <c r="J191">
-        <v>6466</v>
+        <v>280</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311596592</t>
+          <t xml:space="preserve">311601100</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-29</t>
+          <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14366,30 +14366,30 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkmosevej 26</t>
+          <t xml:space="preserve">Nørregade 11A</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">4503146</t>
+          <t xml:space="preserve">5697089</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J192">
-        <v>347</v>
+        <v>1066</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598021</t>
+          <t xml:space="preserve">311601096</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-05</t>
+          <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdemarsvej 343</t>
+          <t xml:space="preserve">Gl. Skolevej 76</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -14451,7 +14451,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704898</t>
+          <t xml:space="preserve">5699373</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -14460,11 +14460,11 @@
         </is>
       </c>
       <c r="J193">
-        <v>15574</v>
+        <v>1547</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598704</t>
+          <t xml:space="preserve">311604976</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-09</t>
+          <t xml:space="preserve">2032-06-02</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandagervej 35</t>
+          <t xml:space="preserve">Bethaniagade 3A</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -14526,20 +14526,20 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700242</t>
+          <t xml:space="preserve">5697356</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J194">
-        <v>904</v>
+        <v>365</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311599479</t>
+          <t xml:space="preserve">311605257</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-11</t>
+          <t xml:space="preserve">2032-06-03</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fenrisvej 24</t>
+          <t xml:space="preserve">Brorsonsvej 12</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5702325</t>
+          <t xml:space="preserve">5706488</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -14610,11 +14610,11 @@
         </is>
       </c>
       <c r="J195">
-        <v>280</v>
+        <v>2761</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601100</t>
+          <t xml:space="preserve">311613717</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14624,7 +14624,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-18</t>
+          <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 11A</t>
+          <t xml:space="preserve">Brorsonsvej 14</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -14676,20 +14676,20 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697089</t>
+          <t xml:space="preserve">5706488</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J196">
-        <v>1066</v>
+        <v>1280</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601096</t>
+          <t xml:space="preserve">311613723</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-18</t>
+          <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Skolevej 76</t>
+          <t xml:space="preserve">Brorsonsvej 16</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14751,20 +14751,20 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699373</t>
+          <t xml:space="preserve">5706488</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J197">
-        <v>1547</v>
+        <v>1280</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311604976</t>
+          <t xml:space="preserve">311613722</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-02</t>
+          <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bethaniagade 3A</t>
+          <t xml:space="preserve">Brorsonsvej 18</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -14826,20 +14826,20 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697356</t>
+          <t xml:space="preserve">5706488</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J198">
-        <v>365</v>
+        <v>1280</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311605257</t>
+          <t xml:space="preserve">311613720</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-03</t>
+          <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brorsonsvej 12</t>
+          <t xml:space="preserve">Rosenholmvej 29</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -14901,20 +14901,20 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706488</t>
+          <t xml:space="preserve">9874254</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J199">
-        <v>2761</v>
+        <v>1070</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311613717</t>
+          <t xml:space="preserve">311613998</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-07</t>
+          <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brorsonsvej 14</t>
+          <t xml:space="preserve">Rosenholmvej 33</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -14976,20 +14976,20 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706488</t>
+          <t xml:space="preserve">9874254</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J200">
-        <v>1280</v>
+        <v>1084</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311613723</t>
+          <t xml:space="preserve">311614001</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-07</t>
+          <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brorsonsvej 16</t>
+          <t xml:space="preserve">Rosenholmvej 35</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -15051,20 +15051,20 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706488</t>
+          <t xml:space="preserve">9874254</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J201">
-        <v>1280</v>
+        <v>2879</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311613722</t>
+          <t xml:space="preserve">311614000</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15074,7 +15074,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-07</t>
+          <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brorsonsvej 18</t>
+          <t xml:space="preserve">Bethaniagade 3B</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -15126,20 +15126,20 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706488</t>
+          <t xml:space="preserve">5697356</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J202">
-        <v>1280</v>
+        <v>1048</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311613720</t>
+          <t xml:space="preserve">311620382</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-07</t>
+          <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -15191,30 +15191,30 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenholmvej 29</t>
+          <t xml:space="preserve">Fuglevænget 1</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">9874254</t>
+          <t xml:space="preserve">4503146</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J203">
-        <v>1070</v>
+        <v>957</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311613998</t>
+          <t xml:space="preserve">311620387</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-08</t>
+          <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -15266,30 +15266,30 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenholmvej 33</t>
+          <t xml:space="preserve">Fuglevænget 1</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">9874254</t>
+          <t xml:space="preserve">4503146</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J204">
-        <v>1084</v>
+        <v>927</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614001</t>
+          <t xml:space="preserve">311620389</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-08</t>
+          <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -15326,12 +15326,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herning Kommune</t>
+          <t xml:space="preserve">bomidtvest</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenholmvej 35</t>
+          <t xml:space="preserve">Bytoften 79</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">9874254</t>
+          <t xml:space="preserve">331825, 331826</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -15360,21 +15360,21 @@
         </is>
       </c>
       <c r="J205">
-        <v>2879</v>
+        <v>781</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614000</t>
+          <t xml:space="preserve">311622284</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-08</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bethaniagade 3B</t>
+          <t xml:space="preserve">Skoletoften 7</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -15426,20 +15426,20 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697356</t>
+          <t xml:space="preserve">4455105</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J206">
-        <v>1048</v>
+        <v>1524</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620382</t>
+          <t xml:space="preserve">311622235</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-15</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -15491,30 +15491,30 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevænget 1</t>
+          <t xml:space="preserve">Skoletoften 7</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">4503146</t>
+          <t xml:space="preserve">4455105</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J207">
-        <v>957</v>
+        <v>1719</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620387</t>
+          <t xml:space="preserve">311622236</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-15</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15566,30 +15566,30 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevænget 1</t>
+          <t xml:space="preserve">Th. Nielsens Gade 25</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">4503146</t>
+          <t xml:space="preserve">5696550</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J208">
-        <v>927</v>
+        <v>653</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620389</t>
+          <t xml:space="preserve">311623523</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-15</t>
+          <t xml:space="preserve">2032-08-26</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15626,12 +15626,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">bomidtvest</t>
+          <t xml:space="preserve">Herning Kommune</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -15641,17 +15641,17 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bytoften 79</t>
+          <t xml:space="preserve">Langgade 16</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7550</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">331825, 331826</t>
+          <t xml:space="preserve">334871, 334872</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -15660,11 +15660,11 @@
         </is>
       </c>
       <c r="J209">
-        <v>781</v>
+        <v>2108</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622284</t>
+          <t xml:space="preserve">311623871</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2032-08-29</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skoletoften 7</t>
+          <t xml:space="preserve">Gilmosevej 20</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -15726,20 +15726,20 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">4455105</t>
+          <t xml:space="preserve">5707304</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J210">
-        <v>1524</v>
+        <v>8928</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622235</t>
+          <t xml:space="preserve">311628842</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2032-09-19</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skoletoften 7</t>
+          <t xml:space="preserve">Baunetoften 101</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -15801,20 +15801,20 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">4455105</t>
+          <t xml:space="preserve">8279488</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J211">
-        <v>1719</v>
+        <v>860</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622236</t>
+          <t xml:space="preserve">311639214</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2032-10-31</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Th. Nielsens Gade 25</t>
+          <t xml:space="preserve">Rosenholmvej 31</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15876,20 +15876,20 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">5696550</t>
+          <t xml:space="preserve">9874254</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J212">
-        <v>653</v>
+        <v>389</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623523</t>
+          <t xml:space="preserve">311639215</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-26</t>
+          <t xml:space="preserve">2032-10-31</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15941,40 +15941,40 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langgade 16</t>
+          <t xml:space="preserve">Lindegårdsvej 3A</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">7550</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">334871, 334872</t>
+          <t xml:space="preserve">5699861</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J213">
-        <v>2108</v>
+        <v>2443</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623871</t>
+          <t xml:space="preserve">311643464</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-29</t>
+          <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gilmosevej 20</t>
+          <t xml:space="preserve">Lindegårdsvej 3B</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -16026,20 +16026,20 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">5707304</t>
+          <t xml:space="preserve">5699861</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J214">
-        <v>8928</v>
+        <v>1548</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311628842</t>
+          <t xml:space="preserve">311643474</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-19</t>
+          <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunetoften 101</t>
+          <t xml:space="preserve">Lindegårdsvej 3D</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -16101,7 +16101,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">8279488</t>
+          <t xml:space="preserve">5699861</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -16110,11 +16110,11 @@
         </is>
       </c>
       <c r="J215">
-        <v>860</v>
+        <v>2443</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311639214</t>
+          <t xml:space="preserve">311643467</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-31</t>
+          <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenholmvej 31</t>
+          <t xml:space="preserve">Lindegårdsvej 5</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -16176,20 +16176,20 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">9874254</t>
+          <t xml:space="preserve">5699861</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J216">
-        <v>389</v>
+        <v>2011</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311639215</t>
+          <t xml:space="preserve">311643469</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-31</t>
+          <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 3A</t>
+          <t xml:space="preserve">Søbysøvej 7</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -16251,20 +16251,20 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699861</t>
+          <t xml:space="preserve">1474174</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J217">
-        <v>2443</v>
+        <v>560</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643464</t>
+          <t xml:space="preserve">311643479</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 3B</t>
+          <t xml:space="preserve">Vestermarken 3</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16326,20 +16326,20 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699861</t>
+          <t xml:space="preserve">4450791</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J218">
-        <v>1548</v>
+        <v>1852</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643474</t>
+          <t xml:space="preserve">311643477</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 3D</t>
+          <t xml:space="preserve">Vestermarken 3</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16401,20 +16401,20 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699861</t>
+          <t xml:space="preserve">4450791</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J219">
-        <v>2443</v>
+        <v>379</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643467</t>
+          <t xml:space="preserve">311643496</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 5</t>
+          <t xml:space="preserve">Lindegårdsvej 3C</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -16481,15 +16481,15 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J220">
-        <v>2011</v>
+        <v>2172</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643469</t>
+          <t xml:space="preserve">311644039</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16541,30 +16541,30 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søbysøvej 7</t>
+          <t xml:space="preserve">Hovedgaden 32</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">6973</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474174</t>
+          <t xml:space="preserve">4425011</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J221">
-        <v>560</v>
+        <v>1644</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643479</t>
+          <t xml:space="preserve">311646026</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-11-30</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16616,30 +16616,30 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestermarken 3</t>
+          <t xml:space="preserve">Hovedgaden 32</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">6973</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450791</t>
+          <t xml:space="preserve">4425011</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J222">
-        <v>1852</v>
+        <v>586</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643477</t>
+          <t xml:space="preserve">311646032</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-11-30</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16691,30 +16691,30 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestermarken 3</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7550</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450791</t>
+          <t xml:space="preserve">4505959</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J223">
-        <v>379</v>
+        <v>4534</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643496</t>
+          <t xml:space="preserve">311649340</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-12-15</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16766,7 +16766,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 3C</t>
+          <t xml:space="preserve">Skolesvinget 3</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -16776,20 +16776,20 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699861</t>
+          <t xml:space="preserve">4457315</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J224">
-        <v>2172</v>
+        <v>1008</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644039</t>
+          <t xml:space="preserve">311652347</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16841,17 +16841,17 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 32</t>
+          <t xml:space="preserve">Nørrevænget 4</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">6973</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">4425011</t>
+          <t xml:space="preserve">4463109</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -16860,11 +16860,11 @@
         </is>
       </c>
       <c r="J225">
-        <v>1644</v>
+        <v>1169</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646026</t>
+          <t xml:space="preserve">311653660</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-30</t>
+          <t xml:space="preserve">2033-01-12</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16916,30 +16916,30 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 32</t>
+          <t xml:space="preserve">Kirkegade 7</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">6973</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">4425011</t>
+          <t xml:space="preserve">4462864</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J226">
-        <v>586</v>
+        <v>724</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646032</t>
+          <t xml:space="preserve">311654163</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-30</t>
+          <t xml:space="preserve">2033-01-16</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16991,30 +16991,30 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Sydgaden 6</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">7550</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">4505959</t>
+          <t xml:space="preserve">329553, 329554</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J227">
-        <v>4534</v>
+        <v>3790</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649340</t>
+          <t xml:space="preserve">311654167</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-15</t>
+          <t xml:space="preserve">2033-01-16</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -17066,17 +17066,17 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolesvinget 3</t>
+          <t xml:space="preserve">Østergade 2</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7490</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">4457315</t>
+          <t xml:space="preserve">334947, 334948</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -17085,11 +17085,11 @@
         </is>
       </c>
       <c r="J228">
-        <v>1008</v>
+        <v>4340</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652347</t>
+          <t xml:space="preserve">311656515</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-04</t>
+          <t xml:space="preserve">2033-01-27</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -17141,17 +17141,17 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevænget 4</t>
+          <t xml:space="preserve">Nørregade 7A</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">4463109</t>
+          <t xml:space="preserve">7168779</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -17160,11 +17160,11 @@
         </is>
       </c>
       <c r="J229">
-        <v>1169</v>
+        <v>1614</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653660</t>
+          <t xml:space="preserve">311661414</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-12</t>
+          <t xml:space="preserve">2033-02-21</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -17216,30 +17216,30 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 7</t>
+          <t xml:space="preserve">Nørregade 7A</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">4462864</t>
+          <t xml:space="preserve">7168779</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J230">
-        <v>724</v>
+        <v>1980</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654163</t>
+          <t xml:space="preserve">311664324</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-16</t>
+          <t xml:space="preserve">2033-03-06</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydgaden 6</t>
+          <t xml:space="preserve">Nørregade 7B</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -17301,20 +17301,20 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">329553, 329554</t>
+          <t xml:space="preserve">7168779</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J231">
-        <v>3790</v>
+        <v>420</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654167</t>
+          <t xml:space="preserve">311664326</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-16</t>
+          <t xml:space="preserve">2033-03-06</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -17366,30 +17366,30 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 2</t>
+          <t xml:space="preserve">Nørregade 7C</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">7490</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">334947, 334948</t>
+          <t xml:space="preserve">7168779</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J232">
-        <v>4340</v>
+        <v>1728</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656515</t>
+          <t xml:space="preserve">311664329</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-27</t>
+          <t xml:space="preserve">2033-03-06</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7A</t>
+          <t xml:space="preserve">Nørregade 7D</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -17456,15 +17456,15 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J233">
-        <v>1614</v>
+        <v>1106</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661414</t>
+          <t xml:space="preserve">311664321</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-21</t>
+          <t xml:space="preserve">2033-03-06</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7A</t>
+          <t xml:space="preserve">Hammerum Hovedgade 14</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -17526,20 +17526,20 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">7168779</t>
+          <t xml:space="preserve">8518026</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J234">
-        <v>1980</v>
+        <v>7138</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664324</t>
+          <t xml:space="preserve">311665603</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -17549,7 +17549,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-06</t>
+          <t xml:space="preserve">2033-03-10</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17576,12 +17576,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herning Kommune</t>
+          <t xml:space="preserve">BOLIGSELSKABET FRUEHØJGAARD</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -17591,7 +17591,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7B</t>
+          <t xml:space="preserve">Kousgaards Plads 4</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -17601,30 +17601,30 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">7168779</t>
+          <t xml:space="preserve">418274, 418275</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J235">
-        <v>420</v>
+        <v>6809</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664326</t>
+          <t xml:space="preserve">311665757</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-06</t>
+          <t xml:space="preserve">2033-03-11</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17651,12 +17651,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herning Kommune</t>
+          <t xml:space="preserve">FællesBo</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -17666,40 +17666,40 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7C</t>
+          <t xml:space="preserve">Skolegade 5</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7490</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">7168779</t>
+          <t xml:space="preserve">334945, 334946</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J236">
-        <v>1728</v>
+        <v>2267</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664329</t>
+          <t xml:space="preserve">311678734</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-06</t>
+          <t xml:space="preserve">2033-05-04</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7D</t>
+          <t xml:space="preserve">Mellemtoften 14</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -17751,20 +17751,20 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">7168779</t>
+          <t xml:space="preserve">4453352</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J237">
-        <v>1106</v>
+        <v>689</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664321</t>
+          <t xml:space="preserve">311698577</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17774,7 +17774,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-06</t>
+          <t xml:space="preserve">2033-08-08</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hammerum Hovedgade 14</t>
+          <t xml:space="preserve">Bethaniagade 30</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -17826,7 +17826,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">8518026</t>
+          <t xml:space="preserve">5697779</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -17835,11 +17835,11 @@
         </is>
       </c>
       <c r="J238">
-        <v>7138</v>
+        <v>1189</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665603</t>
+          <t xml:space="preserve">311698822</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-10</t>
+          <t xml:space="preserve">2033-08-09</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17876,12 +17876,12 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOLIGSELSKABET FRUEHØJGAARD</t>
+          <t xml:space="preserve">Herning Kommune</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -17891,17 +17891,17 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kousgaards Plads 4</t>
+          <t xml:space="preserve">Bjørnkærvej 1A</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">418274, 418275</t>
+          <t xml:space="preserve">9835817</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -17910,21 +17910,21 @@
         </is>
       </c>
       <c r="J239">
-        <v>6809</v>
+        <v>264</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665757</t>
+          <t xml:space="preserve">311702712</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-11</t>
+          <t xml:space="preserve">2033-08-25</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17951,12 +17951,12 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">FællesBo</t>
+          <t xml:space="preserve">Herning Kommune</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -17966,40 +17966,40 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 5</t>
+          <t xml:space="preserve">Bjørnkærvej 1B</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">7490</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">334945, 334946</t>
+          <t xml:space="preserve">9835817</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J240">
-        <v>2267</v>
+        <v>1197</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311678734</t>
+          <t xml:space="preserve">311702713</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-04</t>
+          <t xml:space="preserve">2033-08-25</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -18041,30 +18041,30 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemtoften 14</t>
+          <t xml:space="preserve">Bjørnkærvej 1C</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">4453352</t>
+          <t xml:space="preserve">9835817</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J241">
-        <v>689</v>
+        <v>1225</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698577</t>
+          <t xml:space="preserve">311702714</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-08</t>
+          <t xml:space="preserve">2033-08-25</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -18116,30 +18116,30 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bethaniagade 30</t>
+          <t xml:space="preserve">Bjørnkærvej 1D</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697779</t>
+          <t xml:space="preserve">9835817</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J242">
-        <v>1189</v>
+        <v>825</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698822</t>
+          <t xml:space="preserve">311702715</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-09</t>
+          <t xml:space="preserve">2033-08-25</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -18176,12 +18176,12 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herning Kommune</t>
+          <t xml:space="preserve">FællesBo</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -18191,17 +18191,17 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjørnkærvej 1A</t>
+          <t xml:space="preserve">Nørregade 11</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7280</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">9835817</t>
+          <t xml:space="preserve">335411, 335412</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -18210,21 +18210,21 @@
         </is>
       </c>
       <c r="J243">
-        <v>264</v>
+        <v>2485</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311702712</t>
+          <t xml:space="preserve">311703384</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-25</t>
+          <t xml:space="preserve">2033-08-29</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -18266,30 +18266,30 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjørnkærvej 1B</t>
+          <t xml:space="preserve">Sandagervej 39</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">9835817</t>
+          <t xml:space="preserve">5700223</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J244">
-        <v>1197</v>
+        <v>609</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311702713</t>
+          <t xml:space="preserve">311704121</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-25</t>
+          <t xml:space="preserve">2033-08-31</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -18341,30 +18341,30 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjørnkærvej 1C</t>
+          <t xml:space="preserve">Kollundvej 41</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">9835817</t>
+          <t xml:space="preserve">4453567</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J245">
-        <v>1225</v>
+        <v>589</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311702714</t>
+          <t xml:space="preserve">311704317</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-25</t>
+          <t xml:space="preserve">2033-09-01</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18401,12 +18401,12 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herning Kommune</t>
+          <t xml:space="preserve">Lejerbo,Herning</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -18416,40 +18416,40 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjørnkærvej 1D</t>
+          <t xml:space="preserve">Sabroesvej 9A</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">9835817</t>
+          <t xml:space="preserve">407269, 407270</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J246">
-        <v>825</v>
+        <v>1745</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311702715</t>
+          <t xml:space="preserve">311710650</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-25</t>
+          <t xml:space="preserve">2033-09-27</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18476,12 +18476,12 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">FællesBo</t>
+          <t xml:space="preserve">Herning Kommune</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -18491,17 +18491,17 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 11</t>
+          <t xml:space="preserve">Bethaniagade 6</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">7280</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">335411, 335412</t>
+          <t xml:space="preserve">7952590</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -18510,21 +18510,21 @@
         </is>
       </c>
       <c r="J247">
-        <v>2485</v>
+        <v>308</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311703384</t>
+          <t xml:space="preserve">311712050</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-29</t>
+          <t xml:space="preserve">2033-10-03</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18566,17 +18566,17 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandagervej 39</t>
+          <t xml:space="preserve">Bødkervej 1C</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7451</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700223</t>
+          <t xml:space="preserve">100091782</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -18585,11 +18585,11 @@
         </is>
       </c>
       <c r="J248">
-        <v>609</v>
+        <v>349</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311704121</t>
+          <t xml:space="preserve">311712048</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -18599,7 +18599,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-31</t>
+          <t xml:space="preserve">2033-10-03</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kollundvej 41</t>
+          <t xml:space="preserve">Tolstedvej 22</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -18651,20 +18651,20 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">4453567</t>
+          <t xml:space="preserve">7740155</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J249">
-        <v>589</v>
+        <v>282</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311704317</t>
+          <t xml:space="preserve">311712047</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -18674,7 +18674,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-01</t>
+          <t xml:space="preserve">2033-10-03</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -18701,12 +18701,12 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejerbo,Herning</t>
+          <t xml:space="preserve">Herning Kommune</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sabroesvej 9A</t>
+          <t xml:space="preserve">Gammel Løvbakkevej 2</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">407269, 407270</t>
+          <t xml:space="preserve">329760</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -18735,21 +18735,21 @@
         </is>
       </c>
       <c r="J250">
-        <v>1745</v>
+        <v>703</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710650</t>
+          <t xml:space="preserve">311729072</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-27</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bethaniagade 6</t>
+          <t xml:space="preserve">Gammel Løvbakkevej 2</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18801,20 +18801,20 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">7952590</t>
+          <t xml:space="preserve">329760</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J251">
-        <v>308</v>
+        <v>343</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311712050</t>
+          <t xml:space="preserve">311729073</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-03</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18866,30 +18866,30 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bødkervej 1C</t>
+          <t xml:space="preserve">Trælundvej 1A</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">7451</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">100091782</t>
+          <t xml:space="preserve">329760</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J252">
-        <v>349</v>
+        <v>919</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311712048</t>
+          <t xml:space="preserve">311729074</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -18899,7 +18899,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-03</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tolstedvej 22</t>
+          <t xml:space="preserve">Trælundvej 1A</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -18951,20 +18951,20 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">7740155</t>
+          <t xml:space="preserve">329760</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J253">
-        <v>282</v>
+        <v>717</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311712047</t>
+          <t xml:space="preserve">311729075</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-03</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Løvbakkevej 2</t>
+          <t xml:space="preserve">Studsgårdvej 25A</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -19026,30 +19026,30 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">329760</t>
+          <t xml:space="preserve">100595167</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J254">
-        <v>703</v>
+        <v>410</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729072</t>
+          <t xml:space="preserve">311730337</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-14</t>
+          <t xml:space="preserve">2033-12-20</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -19091,7 +19091,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Løvbakkevej 2</t>
+          <t xml:space="preserve">Gadegårdsvej 121</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -19101,20 +19101,20 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">329760</t>
+          <t xml:space="preserve">9755163</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J255">
-        <v>343</v>
+        <v>6442</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729073</t>
+          <t xml:space="preserve">311731827</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-14</t>
+          <t xml:space="preserve">2034-01-04</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trælundvej 1A</t>
+          <t xml:space="preserve">Markedspladsen 2</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -19176,7 +19176,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">329760</t>
+          <t xml:space="preserve">332592</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -19185,11 +19185,11 @@
         </is>
       </c>
       <c r="J256">
-        <v>919</v>
+        <v>6642</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729074</t>
+          <t xml:space="preserve">311733061</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-14</t>
+          <t xml:space="preserve">2034-01-12</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trælundvej 1A</t>
+          <t xml:space="preserve">Vestergade 92</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -19251,20 +19251,20 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">329760</t>
+          <t xml:space="preserve">5699376</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J257">
-        <v>717</v>
+        <v>9550</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729075</t>
+          <t xml:space="preserve">311737634</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -19274,7 +19274,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-14</t>
+          <t xml:space="preserve">2034-02-07</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -19316,7 +19316,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studsgårdvej 25A</t>
+          <t xml:space="preserve">Skovvænget 2N</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -19326,30 +19326,30 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">100595167</t>
+          <t xml:space="preserve">9827058</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J258">
-        <v>410</v>
+        <v>496</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730337</t>
+          <t xml:space="preserve">311780363</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiOptimo ApS</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-20</t>
+          <t xml:space="preserve">2034-08-26</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gadegårdsvej 121</t>
+          <t xml:space="preserve">Fuglsang Toft 4</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -19401,7 +19401,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">9755163</t>
+          <t xml:space="preserve">100052096</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -19410,11 +19410,11 @@
         </is>
       </c>
       <c r="J259">
-        <v>6442</v>
+        <v>11240</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731827</t>
+          <t xml:space="preserve">311784417</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-04</t>
+          <t xml:space="preserve">2034-09-12</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -19451,12 +19451,12 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herning Kommune</t>
+          <t xml:space="preserve">Fastrupdalen ApS</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Markedspladsen 2</t>
+          <t xml:space="preserve">Fastrupdalen 40</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -19476,30 +19476,30 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">332592</t>
+          <t xml:space="preserve">100684596</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J260">
-        <v>6642</v>
+        <v>4210</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733061</t>
+          <t xml:space="preserve">311790345</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-12</t>
+          <t xml:space="preserve">2034-10-09</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -19541,7 +19541,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 92</t>
+          <t xml:space="preserve">Hammerum Hovedgade 8</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699376</t>
+          <t xml:space="preserve">9949194</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -19560,21 +19560,21 @@
         </is>
       </c>
       <c r="J261">
-        <v>9550</v>
+        <v>314</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737634</t>
+          <t xml:space="preserve">311807464</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-07</t>
+          <t xml:space="preserve">2035-01-23</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvænget 2N</t>
+          <t xml:space="preserve">Gl. Landevej 61</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -19626,20 +19626,20 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">9827058</t>
+          <t xml:space="preserve">9386416</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="J262">
-        <v>496</v>
+        <v>11187</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311780363</t>
+          <t xml:space="preserve">311827530</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-26</t>
+          <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsang Toft 4</t>
+          <t xml:space="preserve">Gl. Landevej 61</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -19701,20 +19701,20 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052096</t>
+          <t xml:space="preserve">9386416</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="J263">
-        <v>11240</v>
+        <v>1164</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311784417</t>
+          <t xml:space="preserve">311827530</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-12</t>
+          <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -19751,12 +19751,12 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fastrupdalen ApS</t>
+          <t xml:space="preserve">Herning Kommune</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fastrupdalen 40</t>
+          <t xml:space="preserve">Gl. Landevej 71</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -19776,30 +19776,30 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">100684596</t>
+          <t xml:space="preserve">9386416</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="J264">
-        <v>4210</v>
+        <v>7390</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790345</t>
+          <t xml:space="preserve">311827530</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-09</t>
+          <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hammerum Hovedgade 8</t>
+          <t xml:space="preserve">Møllegade 16</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -19851,30 +19851,30 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">9949194</t>
+          <t xml:space="preserve">9386416</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="J265">
-        <v>314</v>
+        <v>4622</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311807464</t>
+          <t xml:space="preserve">311827530</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-23</t>
+          <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Landevej 61</t>
+          <t xml:space="preserve">Overgade 22</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -19931,11 +19931,11 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="J266">
-        <v>11187</v>
+        <v>494</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Landevej 61</t>
+          <t xml:space="preserve">Overgade 4</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -20006,11 +20006,11 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="J267">
-        <v>1164</v>
+        <v>1327</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Landevej 71</t>
+          <t xml:space="preserve">Østergade 8</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -20076,20 +20076,20 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">9386416</t>
+          <t xml:space="preserve">5697359</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J268">
-        <v>7390</v>
+        <v>5468</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827530</t>
+          <t xml:space="preserve">311837610</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -20099,7 +20099,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-28</t>
+          <t xml:space="preserve">2035-06-12</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -20141,7 +20141,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllegade 16</t>
+          <t xml:space="preserve">Snejbjerg Hovedgade 75</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -20151,20 +20151,20 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">9386416</t>
+          <t xml:space="preserve">329181</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J269">
-        <v>4622</v>
+        <v>11385</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827530</t>
+          <t xml:space="preserve">311899308</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-28</t>
+          <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overgade 22</t>
+          <t xml:space="preserve">Kousgaards Plads 1</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -20226,20 +20226,20 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">9386416</t>
+          <t xml:space="preserve">329484, 329485, 329486, 329487, 329488, 329489, 329490, 329491, 329492, 329510, 329493, 329494, 329495, 329496, 329497, 329498, 329499, 329500, 329502, 329503, 329504, 329505, 329506, 329507, 329508, 329509</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J270">
-        <v>494</v>
+        <v>18167</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827530</t>
+          <t xml:space="preserve">311858702</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -20249,7 +20249,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-28</t>
+          <t xml:space="preserve">2035-09-29</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overgade 4</t>
+          <t xml:space="preserve">Vesterlindvej 21</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -20301,20 +20301,20 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">9386416</t>
+          <t xml:space="preserve">4452247</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J271">
-        <v>1327</v>
+        <v>264</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827530</t>
+          <t xml:space="preserve">311905571</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-28</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -20351,12 +20351,12 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herning Kommune</t>
+          <t xml:space="preserve">EJENDOMSSELSKABET ÅGÅRDSVEJ 2 ApS</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -20366,17 +20366,17 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 8</t>
+          <t xml:space="preserve">Ågårdsvej 2A</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697359</t>
+          <t xml:space="preserve">334130, 334131, 334132</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -20385,21 +20385,21 @@
         </is>
       </c>
       <c r="J272">
-        <v>5468</v>
+        <v>2352</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311837610</t>
+          <t xml:space="preserve">311913941</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">Lemvig Arkitektkontor Aps</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-12</t>
+          <t xml:space="preserve">2036-07-09</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -20441,30 +20441,30 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snejbjerg Hovedgade 75</t>
+          <t xml:space="preserve">Gyvelvej 5</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7550</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">329181</t>
+          <t xml:space="preserve">4506406</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J273">
-        <v>11385</v>
+        <v>498</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311899308</t>
+          <t xml:space="preserve">311928799</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -20474,7 +20474,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-26</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kousgaards Plads 1</t>
+          <t xml:space="preserve">Haugevej 25</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -20526,7 +20526,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">329484, 329485, 329486, 329487, 329488, 329489, 329490, 329491, 329492, 329510, 329493, 329494, 329495, 329496, 329497, 329498, 329499, 329500, 329502, 329503, 329504, 329505, 329506, 329507, 329508, 329509</t>
+          <t xml:space="preserve">100063131</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -20535,11 +20535,11 @@
         </is>
       </c>
       <c r="J274">
-        <v>18167</v>
+        <v>1683</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858702</t>
+          <t xml:space="preserve">311928800</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20549,7 +20549,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-29</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -20591,30 +20591,30 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterlindvej 21</t>
+          <t xml:space="preserve">Skolevejen 6</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">4452247</t>
+          <t xml:space="preserve">4455442</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J275">
-        <v>264</v>
+        <v>2812</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905571</t>
+          <t xml:space="preserve">311928795</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -20624,7 +20624,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -20651,12 +20651,12 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">EJENDOMSSELSKABET ÅGÅRDSVEJ 2 ApS</t>
+          <t xml:space="preserve">Herning Kommune</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -20666,40 +20666,40 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågårdsvej 2A</t>
+          <t xml:space="preserve">Skolevejen 6</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">334130, 334131, 334132</t>
+          <t xml:space="preserve">4455442</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J276">
-        <v>2352</v>
+        <v>386</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311913941</t>
+          <t xml:space="preserve">311928797</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lemvig Arkitektkontor Aps</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-09</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
